--- a/Phase 2 - Language Definition/language definition.xlsx
+++ b/Phase 2 - Language Definition/language definition.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Desktop\KG project\KG-2025-26-UniTn-Project\Phase 3 - Formal Modeling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Desktop\KG project\KG-2025-26-UniTn-Project\Phase 2 - Language Definition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D84280-76B2-4BC3-94CE-592409A9C01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557BFF0F-B167-47CD-AA41-D31387329703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253035B1-88A8-46D5-9D92-9265E858590C}"/>
   </bookViews>
@@ -38,15 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
-    <t>English Word</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Italian Word</t>
-  </si>
-  <si>
     <t>institute</t>
   </si>
   <si>
@@ -95,12 +86,6 @@
     <t>educational coordinator</t>
   </si>
   <si>
-    <t>URL EN</t>
-  </si>
-  <si>
-    <t>URL IT</t>
-  </si>
-  <si>
     <t>surface</t>
   </si>
   <si>
@@ -369,6 +354,21 @@
   </si>
   <si>
     <t>high school</t>
+  </si>
+  <si>
+    <t>Word-EN</t>
+  </si>
+  <si>
+    <t>Glossary-EN</t>
+  </si>
+  <si>
+    <t>URL-EN</t>
+  </si>
+  <si>
+    <t>URL-IT</t>
+  </si>
+  <si>
+    <t>Word-IT</t>
   </si>
 </sst>
 </file>
@@ -778,394 +778,394 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="B22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
